--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0001T0006Z000C1N72_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0001T0006Z000C1N72_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.78826121169488</v>
+        <v>4.028092446900418</v>
       </c>
       <c r="D2" t="n">
-        <v>24.43971047324607</v>
+        <v>3.971452951902486</v>
       </c>
       <c r="E2" t="n">
-        <v>9.667892365336861</v>
+        <v>1.57103250936724</v>
       </c>
       <c r="F2" t="n">
-        <v>9.584079678502256</v>
+        <v>1.557412947756617</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>8.940877108951884</v>
+        <v>1.452892530204681</v>
       </c>
       <c r="D3" t="n">
-        <v>9.485743567007134</v>
+        <v>1.541433329638659</v>
       </c>
       <c r="E3" t="n">
-        <v>9.667892365336861</v>
+        <v>1.57103250936724</v>
       </c>
       <c r="F3" t="n">
-        <v>9.584079678502256</v>
+        <v>1.557412947756617</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>18.35457098472235</v>
+        <v>2.982617785017382</v>
       </c>
       <c r="D4" t="n">
-        <v>17.92362951311073</v>
+        <v>2.912589795880493</v>
       </c>
       <c r="E4" t="n">
-        <v>9.667892365336861</v>
+        <v>1.57103250936724</v>
       </c>
       <c r="F4" t="n">
-        <v>9.584079678502256</v>
+        <v>1.557412947756617</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.18747085049192</v>
+        <v>4.255464013204938</v>
       </c>
       <c r="D5" t="n">
-        <v>25.68006712094385</v>
+        <v>4.173010907153376</v>
       </c>
       <c r="E5" t="n">
-        <v>9.667892365336861</v>
+        <v>1.57103250936724</v>
       </c>
       <c r="F5" t="n">
-        <v>9.584079678502256</v>
+        <v>1.557412947756617</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>16.92287461868751</v>
+        <v>2.74996712553672</v>
       </c>
       <c r="D6" t="n">
-        <v>17.35464363638689</v>
+        <v>2.82012959091287</v>
       </c>
       <c r="E6" t="n">
-        <v>9.667892365336861</v>
+        <v>1.57103250936724</v>
       </c>
       <c r="F6" t="n">
-        <v>9.584079678502256</v>
+        <v>1.557412947756617</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.86054242949436</v>
+        <v>6.152338144792833</v>
       </c>
       <c r="D7" t="n">
-        <v>38.27008901774495</v>
+        <v>6.218889465383555</v>
       </c>
       <c r="E7" t="n">
-        <v>9.667892365336861</v>
+        <v>1.57103250936724</v>
       </c>
       <c r="F7" t="n">
-        <v>9.584079678502256</v>
+        <v>1.557412947756617</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>28.94779191854938</v>
+        <v>4.704016186764274</v>
       </c>
       <c r="D8" t="n">
-        <v>29.31067233178289</v>
+        <v>4.762984253914721</v>
       </c>
       <c r="E8" t="n">
-        <v>9.667892365336861</v>
+        <v>1.57103250936724</v>
       </c>
       <c r="F8" t="n">
-        <v>9.584079678502256</v>
+        <v>1.557412947756617</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>39.0769356698217</v>
+        <v>6.350002046346026</v>
       </c>
       <c r="D9" t="n">
-        <v>38.79722646185891</v>
+        <v>6.304549300052073</v>
       </c>
       <c r="E9" t="n">
-        <v>9.667892365336861</v>
+        <v>1.57103250936724</v>
       </c>
       <c r="F9" t="n">
-        <v>9.584079678502256</v>
+        <v>1.557412947756617</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
